--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154029</v>
+        <v>128207452</v>
       </c>
       <c r="B4" t="n">
         <v>98468</v>
@@ -935,29 +935,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovberget, Hovberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627880</v>
+        <v>627835</v>
       </c>
       <c r="R4" t="n">
         <v>6921206</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,62 +1014,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154131</v>
+        <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98385</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovberget, Hovberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627900</v>
+        <v>627813</v>
       </c>
       <c r="R5" t="n">
-        <v>6921229</v>
+        <v>6921192</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,6 +1118,564 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128206989</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>627833</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6921208</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128207514</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hovberget, Hovberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>627815</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6921202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128154029</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>627880</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6921206</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128154131</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98385</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627900</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6921229</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128207698</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627892</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6921199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153743</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128153708</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128154029</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128154131</v>
       </c>
       <c r="B9" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128207452</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128206962</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128206989</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128207514</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128207698</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128153743</v>
+        <v>128154131</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627828</v>
+        <v>627900</v>
       </c>
       <c r="R2" t="n">
-        <v>6921202</v>
+        <v>6921229</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,57 +796,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128153708</v>
+        <v>128207183</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627835</v>
+        <v>627854</v>
       </c>
       <c r="R3" t="n">
-        <v>6921202</v>
+        <v>6921168</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128207452</v>
+        <v>128153708</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,20 +931,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hovberget, Hovberget, Mpd</t>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>627835</v>
       </c>
       <c r="R4" t="n">
-        <v>6921206</v>
+        <v>6921202</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128206962</v>
+        <v>128153743</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,20 +1047,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hovberget, Hovberget, Mpd</t>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627813</v>
+        <v>627828</v>
       </c>
       <c r="R5" t="n">
-        <v>6921192</v>
+        <v>6921202</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128206989</v>
+        <v>128154029</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,20 +1163,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hovberget, Hovberget, Mpd</t>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627833</v>
+        <v>627880</v>
       </c>
       <c r="R6" t="n">
-        <v>6921208</v>
+        <v>6921206</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,22 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128207514</v>
+        <v>128206962</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627815</v>
+        <v>627813</v>
       </c>
       <c r="R7" t="n">
-        <v>6921202</v>
+        <v>6921192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128154029</v>
+        <v>128206989</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,29 +1386,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovberget, Hovberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627880</v>
+        <v>627833</v>
       </c>
       <c r="R8" t="n">
-        <v>6921206</v>
+        <v>6921208</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,22 +1423,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,62 +1465,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128154131</v>
+        <v>128207452</v>
       </c>
       <c r="B9" t="n">
-        <v>98509</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovberget, Hovberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627900</v>
+        <v>627835</v>
       </c>
       <c r="R9" t="n">
-        <v>6921229</v>
+        <v>6921206</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128207698</v>
+        <v>128207514</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,14 +1603,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+          <t>Hovberget, Hovberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627892</v>
+        <v>627815</v>
       </c>
       <c r="R10" t="n">
-        <v>6921199</v>
+        <v>6921202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,6 +1676,113 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128207698</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hovbergsstugan, Hovbergsstugan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627892</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6921199</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36072-2025 artfynd.xlsx
+++ b/artfynd/A 36072-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128207183</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128153708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128153743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128206962</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128206989</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128207452</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128207514</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,8 +1833,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128207698</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>